--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_264_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_264_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7708</v>
+        <v>3.2893</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8888</v>
+        <v>3.3737</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.118</v>
+        <v>-0.0844</v>
       </c>
       <c r="G2" t="n">
         <v>1.3174</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1312</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2072</v>
+        <v>0.6921</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V2" t="n">
         <v>0.3943</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6548</v>
+        <v>1.8505</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3767</v>
+        <v>2.3327</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7219</v>
+        <v>-0.4822</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6086</v>
+        <v>0.3275</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5847</v>
+        <v>-0.8333</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0239</v>
+        <v>1.1608</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0948</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8066</v>
+        <v>-1.1757</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2882</v>
+        <v>1.8467</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4862</v>
+        <v>-0.3434</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.222</v>
+        <v>0.3424</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2643</v>
+        <v>-0.6859</v>
       </c>
       <c r="P3" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5643</v>
+        <v>0.0048</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2819</v>
+        <v>0.0868</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2825</v>
+        <v>-0.0819</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.7501</v>
+        <v>1.7501</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.8945</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7501</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3964</v>
+        <v>1.6473</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7541</v>
+        <v>2.1394</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3577</v>
+        <v>-0.4921</v>
       </c>
       <c r="G4" t="n">
         <v>1.4143</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3374</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5895</v>
+        <v>-0.2043</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2522</v>
+        <v>0.1177</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6178</v>
+        <v>1.3472</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1336</v>
+        <v>0.3674</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5158</v>
+        <v>0.9798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3275</v>
+        <v>0.1922</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8333</v>
+        <v>0.0384</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1608</v>
+        <v>0.1539</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1757</v>
+        <v>0.1246</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8467</v>
+        <v>0.5754</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3434</v>
+        <v>-0.5078</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3424</v>
+        <v>-0.0862</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6859</v>
+        <v>-0.4216</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2278</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1123</v>
+        <v>0.291</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1155</v>
+        <v>0.2377</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7501</v>
+        <v>0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>3.8945</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5411</v>
+        <v>0.8344</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9808</v>
+        <v>2.6571</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5219</v>
+        <v>-1.8227</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6431</v>
+        <v>1.6086</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4921</v>
+        <v>0.5847</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.151</v>
+        <v>1.0239</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8789</v>
+        <v>2.0948</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4166</v>
+        <v>0.8066</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4623</v>
+        <v>1.2882</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2358</v>
+        <v>-0.4862</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0755</v>
+        <v>-0.222</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3113</v>
+        <v>-0.2643</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3286</v>
+        <v>0.744</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1019</v>
+        <v>0.5623</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4305</v>
+        <v>0.1817</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3318</v>
+        <v>0.008</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4464</v>
+        <v>-2.1106</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7781</v>
+        <v>2.1187</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1922</v>
+        <v>-1.6431</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0384</v>
+        <v>-0.4921</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1539</v>
+        <v>-1.151</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7000999999999999</v>
+        <v>-1.8789</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1246</v>
+        <v>-0.4166</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5754</v>
+        <v>-1.4623</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5078</v>
+        <v>0.2358</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0862</v>
+        <v>-0.0755</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4216</v>
+        <v>0.3113</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4867</v>
+        <v>-0.2045</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5228</v>
+        <v>-0.2317</v>
       </c>
       <c r="U7" t="n">
-        <v>0.036</v>
+        <v>0.0272</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1437</v>
+        <v>-0.101</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5329</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3892</v>
+        <v>-0.7144</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0809</v>
+        <v>0.4333</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3339</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4148</v>
+        <v>1.1043</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5279</v>
+        <v>-0.4166</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3143</v>
+        <v>1.2146</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7613</v>
+        <v>-0.3646</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8618</v>
+        <v>-0.2543</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1005</v>
+        <v>-0.1103</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3448</v>
+        <v>-0.6398</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3541</v>
+        <v>-0.1845</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0092</v>
+        <v>-0.4553</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7501</v>
+        <v>-1.7501</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3929</v>
+        <v>-0.1788</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8362000000000001</v>
+        <v>0.347</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4434</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0056</v>
+        <v>-0.3468</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1094</v>
+        <v>-0.9423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1038</v>
+        <v>0.5955</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1346</v>
+        <v>0.2644</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1849</v>
+        <v>-0.7527</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0502</v>
+        <v>1.0171</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.129</v>
+        <v>-0.6112</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0755</v>
+        <v>-0.1896</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0535</v>
+        <v>-0.4216</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1889</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5364</v>
+        <v>0.0854</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3558</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.429</v>
+        <v>-0.3146</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1976</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6264999999999999</v>
+        <v>0.4228</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3468</v>
+        <v>0.0809</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9423</v>
+        <v>-0.3339</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5955</v>
+        <v>0.4148</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2644</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7527</v>
+        <v>0.5279</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0171</v>
+        <v>0.3143</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6112</v>
+        <v>-0.7613</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1896</v>
+        <v>-0.8618</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4216</v>
+        <v>0.1005</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0668</v>
+        <v>0.1496</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0154</v>
+        <v>0.0244</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9483</v>
+        <v>-0.4116</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7433</v>
+        <v>-0.6869</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6916</v>
+        <v>0.2753</v>
       </c>
       <c r="G11" t="n">
-        <v>0.43</v>
+        <v>0.0056</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5414</v>
+        <v>0.1094</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1113</v>
+        <v>-0.1038</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7627</v>
+        <v>0.1346</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1881</v>
+        <v>0.1849</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4255</v>
+        <v>-0.0502</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3326</v>
+        <v>-0.129</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3532</v>
+        <v>-0.0755</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6859</v>
+        <v>-0.0535</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1797</v>
+        <v>0.7066</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0193</v>
+        <v>0.3383</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1603</v>
+        <v>0.3684</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.8223</v>
+        <v>-1.3558</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8223</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9649</v>
+        <v>-0.6399</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0824</v>
+        <v>1.0853</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8824</v>
+        <v>-1.7252</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4333</v>
+        <v>0.43</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6709000000000001</v>
+        <v>2.5414</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1043</v>
+        <v>-2.1113</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7627</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4166</v>
+        <v>2.1881</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2146</v>
+        <v>-1.4255</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3646</v>
+        <v>-0.3326</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2543</v>
+        <v>0.3532</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1103</v>
+        <v>-0.6859</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5037</v>
+        <v>0.1287</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8804</v>
+        <v>0.3227</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6234</v>
+        <v>-0.1939</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7501</v>
+        <v>-2.8223</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7501</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2164</v>
+        <v>-5.4995</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0755</v>
+        <v>-5.6274</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1409</v>
+        <v>0.1279</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8038</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0236</v>
+        <v>-0.3066</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3848</v>
+        <v>0.0633</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6387</v>
+        <v>-0.3699</v>
       </c>
       <c r="V13" t="n">
         <v>0.9304</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7825000000000006</v>
+        <v>1.831299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.139899999999997</v>
+        <v>3.753700000000002</v>
       </c>
       <c r="F14" t="n">
         <v>-1.9222</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01610000000000023</v>
+        <v>0.01609999999999978</v>
       </c>
       <c r="H14" t="n">
         <v>-0.7862</v>
@@ -1519,22 +1519,22 @@
         <v>0.8027000000000006</v>
       </c>
       <c r="J14" t="n">
-        <v>5.539999999999999</v>
+        <v>5.540000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>1.8105</v>
       </c>
       <c r="L14" t="n">
-        <v>3.729600000000001</v>
+        <v>3.7296</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.523600000000001</v>
+        <v>-5.5236</v>
       </c>
       <c r="N14" t="n">
         <v>-2.597</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.9269</v>
+        <v>-2.926900000000001</v>
       </c>
       <c r="P14" t="n">
         <v>3.4794</v>
@@ -1546,10 +1546,10 @@
         <v>16.2367</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7468000000000001</v>
+        <v>1.8671</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6456999999999997</v>
+        <v>1.9682</v>
       </c>
       <c r="U14" t="n">
         <v>-0.1009</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4593</v>
+        <v>6.3471</v>
       </c>
       <c r="E15" t="n">
-        <v>3.951</v>
+        <v>4.6587</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5083</v>
+        <v>1.6884</v>
       </c>
       <c r="G15" t="n">
         <v>2.1241</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1133</v>
+        <v>0.7745</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7231</v>
+        <v>-0.0154</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6098</v>
+        <v>0.7899</v>
       </c>
       <c r="V15" t="n">
         <v>3.2166</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1362</v>
+        <v>3.978</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2042</v>
+        <v>1.4656</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9321</v>
+        <v>2.5125</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6619</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3719</v>
+        <v>-1.5559</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0338</v>
+        <v>2.4526</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1849</v>
+        <v>0.4646</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1113</v>
+        <v>-0.9439</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>1.4085</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8468</v>
+        <v>0.4322</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2606</v>
+        <v>-0.612</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1074</v>
+        <v>1.0441</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8187</v>
+        <v>0.3312</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5217</v>
+        <v>-0.1254</v>
       </c>
       <c r="U16" t="n">
-        <v>0.297</v>
+        <v>0.4567</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3558</v>
+        <v>2.2862</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4975</v>
+        <v>2.2862</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6464</v>
+        <v>3.6759</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3476</v>
+        <v>2.4965</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2987</v>
+        <v>1.1794</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8967000000000001</v>
+        <v>-0.6619</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5559</v>
+        <v>0.3719</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4526</v>
+        <v>-1.0338</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4646</v>
+        <v>0.1849</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9439</v>
+        <v>0.1113</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4085</v>
+        <v>0.0736</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4322</v>
+        <v>-0.8468</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.612</v>
+        <v>0.2606</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0441</v>
+        <v>-1.1074</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0004</v>
+        <v>1.3583</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2434</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2429</v>
+        <v>0.5443</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2862</v>
+        <v>1.3558</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2862</v>
+        <v>1.4975</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1342</v>
+        <v>2.4715</v>
       </c>
       <c r="E18" t="n">
-        <v>2.082</v>
+        <v>1.3267</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0522</v>
+        <v>1.1448</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0108</v>
+        <v>2.9256</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0733</v>
+        <v>1.0384</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0841</v>
+        <v>1.8872</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3829</v>
+        <v>2.9865</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9915</v>
+        <v>1.1462</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3914</v>
+        <v>1.8402</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3937</v>
+        <v>-0.0608</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0818</v>
+        <v>-0.1078</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4755</v>
+        <v>0.047</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1476</v>
+        <v>-0.8305</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5149</v>
+        <v>-0.4125</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6625</v>
+        <v>-0.418</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>2.3994</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.4359</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.0365</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.0108</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.0733</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.0841</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.3829</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.3937</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.4755</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.8556</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.8556</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.161</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.214</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.6189</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5951</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.9256</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.0384</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8872</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.9865</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.1462</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.8402</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-0.0608</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.1078</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.6959</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-2.3195</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.6237</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-2.088</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-1.1202</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.9678</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.0722</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.0722</v>
-      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5836</v>
+        <v>0.2126</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8848</v>
+        <v>0.413</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3012</v>
+        <v>-0.2004</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1206</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4722</v>
+        <v>0.1013</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5635</v>
+        <v>-0.7443</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2927</v>
+        <v>-1.0005</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2708</v>
+        <v>0.2562</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3056</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2034</v>
+        <v>0.0226</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8417</v>
+        <v>0.134</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6383</v>
+        <v>-0.1114</v>
       </c>
       <c r="V21" t="n">
         <v>0.9304</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0169</v>
+        <v>-2.878</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8989</v>
+        <v>-4.4436</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9158</v>
+        <v>1.5656</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2377</v>
+        <v>-0.1342</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7058</v>
+        <v>0.7993</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9435</v>
+        <v>-0.9336</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5917</v>
+        <v>1.086</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1104</v>
+        <v>-0.7163</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9398</v>
+        <v>-0.5039</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1141</v>
+        <v>-0.2866</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0539</v>
+        <v>-0.2173</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>-4.1751</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R22" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7415</v>
+        <v>0.4698</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1968</v>
+        <v>0.0239</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5447</v>
+        <v>0.4459</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.7527</v>
+        <v>0.9615</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.9615</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.7527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5122</v>
+        <v>-3.2021</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5616</v>
+        <v>0.7809</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0494</v>
+        <v>-3.983</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1342</v>
+        <v>-0.2377</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7993</v>
+        <v>0.7058</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9336</v>
+        <v>-0.9435</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3697</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>1.086</v>
+        <v>0.5917</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7163</v>
+        <v>0.1104</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5039</v>
+        <v>-0.9398</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2866</v>
+        <v>0.1141</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2173</v>
+        <v>-1.0539</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.1751</v>
+        <v>0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1643</v>
+        <v>0.5564</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.094</v>
+        <v>0.0788</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0703</v>
+        <v>0.4775</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9615</v>
+        <v>-3.7527</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9615</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4531</v>
+        <v>-4.2172</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-3.5967</v>
@@ -2326,10 +2326,10 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6291</v>
+        <v>-0.3932</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U24" t="n">
         <v>0.0431</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8457</v>
+        <v>-4.9015</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3545</v>
+        <v>-5.5904</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5088</v>
+        <v>0.6889</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9748</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3585</v>
+        <v>0.3027</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3462</v>
+        <v>0.1103</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0123</v>
+        <v>0.1924</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6778999999999999</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7822999999999993</v>
+        <v>3.141399999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>1.922200000000001</v>
+        <v>1.922300000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1399</v>
+        <v>1.219199999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.01639999999999997</v>
+        <v>-0.01640000000000086</v>
       </c>
       <c r="H26" t="n">
         <v>0.7861999999999998</v>
@@ -2455,16 +2455,16 @@
         <v>-0.8029000000000002</v>
       </c>
       <c r="J26" t="n">
-        <v>5.523700000000002</v>
+        <v>5.5237</v>
       </c>
       <c r="K26" t="n">
-        <v>2.597</v>
+        <v>2.597000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>2.9266</v>
+        <v>2.926600000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.539999999999999</v>
+        <v>-5.54</v>
       </c>
       <c r="N26" t="n">
         <v>-1.8107</v>
@@ -2482,16 +2482,16 @@
         <v>12.7576</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7467999999999999</v>
+        <v>3.1058</v>
       </c>
       <c r="T26" t="n">
         <v>0.101</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6458</v>
+        <v>3.0049</v>
       </c>
       <c r="V26" t="n">
-        <v>3.5313</v>
+        <v>3.531300000000001</v>
       </c>
       <c r="W26" t="n">
         <v>12.5342</v>
